--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -2744,6 +2744,154 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.003114131309053049</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2777,7 +2925,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -2860,7 +3008,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2870,7 +3018,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -2922,7 +3070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>251</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -2892,6 +2892,151 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3008,7 +3153,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -3018,7 +3163,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -3070,7 +3215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -2334,12 +2334,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2373,81 +2373,92 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.01355270280196709</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2474,17 +2485,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2509,93 +2520,179 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.004812748386718348</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2657,22 +2754,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2802,25 +2899,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="O16" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.003114131309053049</v>
+        <v>0.004812748386718348</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2920,118 +3017,1971 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>D056</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Streptococcus suis</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>人感染猪链球菌病</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="N24" t="n">
+        <v>44</v>
+      </c>
+      <c r="O24" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.003114131309053049</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="n">
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr">
+      <c r="AV27" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr">
+      <c r="BA27" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BB27" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -3153,7 +5103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -3163,7 +5113,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -3183,7 +5133,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3193,7 +5143,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3215,7 +5165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1214,6 +1229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1507,6 +1532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1655,6 +1685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1800,6 +1835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1948,6 +1988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2093,6 +2138,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2241,6 +2291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2776,6 +2831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2924,6 +2984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4239,6 +4304,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4387,6 +4457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +4995,11 @@
       <c r="S27" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">

--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -874,12 +874,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -918,12 +918,14 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -933,66 +935,70 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1025,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1054,29 +1060,48 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.001981719923942849</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1084,68 +1109,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1294,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01355270280196709</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1357,25 +1444,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001203187096679587</v>
+        <v>0.001981719923942849</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1480,12 +1567,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1510,12 +1597,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1524,12 +1611,14 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1539,66 +1628,70 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1625,17 +1718,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1660,29 +1753,48 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.001627841366095912</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1690,68 +1802,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1987,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1963,25 +2137,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002335598481789786</v>
+        <v>0.001203187096679587</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2086,12 +2260,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2116,12 +2290,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2130,12 +2304,14 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2145,66 +2321,70 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2411,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2266,29 +2446,48 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.003892664136316311</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2296,68 +2495,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2650,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2419,28 +2680,26 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2450,70 +2709,66 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2540,17 +2795,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2575,48 +2830,29 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>人感染猪链球菌病</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>23</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.001627841366095912</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2624,130 +2860,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>country:CN-JS:national</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN14" t="b">
-        <v>1</v>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2953,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2809,95 +2983,101 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.01355270280196709</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2924,17 +3104,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2959,29 +3139,48 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.004812748386718348</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2989,68 +3188,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3343,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CN-FJ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fujian, China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3112,28 +3373,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3143,70 +3402,66 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3488,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CN-FJ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fujian, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3268,48 +3523,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>人感染猪链球菌病</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>33</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.002335598481789786</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3317,130 +3553,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:CN-FJ:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3646,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3502,19 +3676,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3591,7 +3765,7 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -3628,12 +3802,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3658,19 +3832,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3714,7 +3888,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-GX:national</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3825,7 +3999,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -3862,12 +4036,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3892,12 +4066,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3981,7 +4155,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -4018,12 +4192,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4048,12 +4222,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4104,7 +4278,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-JX:national</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -4215,7 +4389,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -4252,12 +4426,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4282,12 +4456,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4296,12 +4470,14 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -4311,66 +4487,70 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -4397,17 +4577,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4432,29 +4612,48 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="R24" t="n">
-        <v>0.003114131309053049</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4462,68 +4661,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4816,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4585,12 +4846,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4599,14 +4860,12 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4616,70 +4875,66 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4706,17 +4961,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4741,179 +4996,98 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N26" t="n">
+        <v>55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
+        <v>0.003892664136316311</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>人感染猪链球菌病</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>country:CN-JS:national</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
-        </is>
-      </c>
-      <c r="AT26" t="n">
-        <v>1</v>
-      </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -4945,125 +5119,6191 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>14</v>
+      </c>
+      <c r="O27" t="n">
+        <v>14</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>14</v>
+      </c>
+      <c r="O28" t="n">
+        <v>14</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:CN-JX:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>D056</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Streptococcus suis</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>人感染猪链球菌病</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>68</v>
+      </c>
+      <c r="O36" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.004812748386718348</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>20</v>
+      </c>
+      <c r="O39" t="n">
+        <v>20</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="n">
+        <v>20</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>country:CN-JX:national</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N48" t="n">
+        <v>44</v>
+      </c>
+      <c r="O48" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.003114131309053049</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" t="n">
+        <v>14</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>14</v>
+      </c>
+      <c r="O50" t="n">
+        <v>14</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
         <v>0.01355270280196709</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AP55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="n">
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AU55" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV27" t="inlineStr">
+      <c r="AV55" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="AW27" t="inlineStr">
+      <c r="AW55" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AY55" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="BA27" t="inlineStr">
+      <c r="BA55" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr">
+      <c r="BB55" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BC55" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>10</v>
+      </c>
+      <c r="O56" t="n">
+        <v>10</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>10</v>
+      </c>
+      <c r="O57" t="n">
+        <v>10</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Human Streptococcus suis infection only; excludes animal disease and other streptococcal infections.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_STREPTOCOCCUS_SUIS</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -5100,7 +11340,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -5183,7 +11423,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -5193,7 +11433,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -5213,7 +11453,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -5245,7 +11485,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>310</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d056/2026-2029.xlsx
+++ b/diseases/d056/2026-2029.xlsx
@@ -1047,6 +1047,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,13 +1064,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1461,6 +1476,11 @@
       <c r="R7" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,13 +1493,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1875,6 +1905,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,13 +1922,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2289,6 +2334,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,13 +2351,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2985,6 +3045,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2997,13 +3062,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3822,6 +3897,11 @@
       <c r="R24" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3834,13 +3914,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4800,6 +4890,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4812,13 +4907,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5496,6 +5601,11 @@
       <c r="R36" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5508,13 +5618,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5835,6 +5955,156 @@
       <c r="BC38" t="inlineStr">
         <is>
           <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>streptococcus-suis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -5964,7 +6234,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -6016,7 +6286,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
